--- a/tame_output/ON/bt/strategyON_20231101.xlsx
+++ b/tame_output/ON/bt/strategyON_20231101.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.4%</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.8%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.3%</t>
+          <t>132.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-30</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.3%</t>
+          <t>126.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.3%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1767"/>
+  <dimension ref="A1:G1768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42151,7 +42151,7 @@
         <v>45229</v>
       </c>
       <c r="B1767" t="n">
-        <v>3.056705830556029</v>
+        <v>3.053640504831979</v>
       </c>
       <c r="C1767" t="n">
         <v>3.033268356072139</v>
@@ -42167,6 +42167,29 @@
       </c>
       <c r="G1767" t="n">
         <v>4.331930737459857</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="2" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B1768" t="n">
+        <v>3.059920372423617</v>
+      </c>
+      <c r="C1768" t="n">
+        <v>3.034928653249013</v>
+      </c>
+      <c r="D1768" t="n">
+        <v>1.544712235750095</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>3.652457123235304</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>2.164437302312861</v>
+      </c>
+      <c r="G1768" t="n">
+        <v>4.333591034636732</v>
       </c>
     </row>
   </sheetData>
